--- a/artfynd/A 5800-2026 artfynd.xlsx
+++ b/artfynd/A 5800-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2203,6 +2203,785 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131507935</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91781</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Holmtorp, Holmtorp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>467374</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6572837</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131509684</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Holmtorp, Holmtorp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>467374</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6572837</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131521671</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Holmtorp, Karlskoga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>467173</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6572829</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska gnagspår</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131512700</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Holmtorp, Holmtorp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>467165</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6572886</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Camilla Berglund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Camilla Berglund, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131511446</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97888</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ängarna, Ängarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>467074</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6572539</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131521661</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Holmtorp, Karlskoga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>467347</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6572707</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131521670</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Holmtorp, Karlskoga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>467249</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6572853</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska gnagspår</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5800-2026 artfynd.xlsx
+++ b/artfynd/A 5800-2026 artfynd.xlsx
@@ -2208,7 +2208,7 @@
         <v>131507935</v>
       </c>
       <c r="B17" t="n">
-        <v>91781</v>
+        <v>91784</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>131509684</v>
       </c>
       <c r="B18" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>131512700</v>
       </c>
       <c r="B20" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>131511446</v>
       </c>
       <c r="B21" t="n">
-        <v>97888</v>
+        <v>97891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>131521661</v>
       </c>
       <c r="B22" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 5800-2026 artfynd.xlsx
+++ b/artfynd/A 5800-2026 artfynd.xlsx
@@ -2208,7 +2208,7 @@
         <v>131507935</v>
       </c>
       <c r="B17" t="n">
-        <v>91784</v>
+        <v>91785</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>131509684</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>131512700</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>131511446</v>
       </c>
       <c r="B21" t="n">
-        <v>97891</v>
+        <v>97892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>131521661</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 5800-2026 artfynd.xlsx
+++ b/artfynd/A 5800-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129678389</v>
+        <v>131521663</v>
       </c>
       <c r="B2" t="n">
-        <v>105881</v>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmtorp, Vrm</t>
+          <t>Holmtorp, Karlskoga, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467420</v>
+        <v>467244</v>
       </c>
       <c r="R2" t="n">
-        <v>6572771</v>
+        <v>6572972</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -758,28 +754,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129678335</v>
+        <v>129678333</v>
       </c>
       <c r="B3" t="n">
-        <v>5177</v>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -815,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467054</v>
+        <v>467000</v>
       </c>
       <c r="R3" t="n">
-        <v>6572517</v>
+        <v>6572554</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -851,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129678366</v>
+        <v>129678336</v>
       </c>
       <c r="B4" t="n">
-        <v>96161</v>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -921,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467187</v>
+        <v>467003</v>
       </c>
       <c r="R4" t="n">
-        <v>6572895</v>
+        <v>6572534</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,17 +968,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Emilia Sundell, Hannes Byström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129678333</v>
+        <v>129678366</v>
       </c>
       <c r="B5" t="n">
-        <v>96051</v>
+        <v>96458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,21 +986,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1022,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467000</v>
+        <v>467187</v>
       </c>
       <c r="R5" t="n">
-        <v>6572554</v>
+        <v>6572895</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1077,17 +1069,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emilia Sundell, Hannes Byström</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129678336</v>
+        <v>131507935</v>
       </c>
       <c r="B6" t="n">
-        <v>96051</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,38 +1087,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Holmtorp, Vrm</t>
+          <t>Holmtorp, Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467003</v>
+        <v>467374</v>
       </c>
       <c r="R6" t="n">
-        <v>6572534</v>
+        <v>6572837</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,12 +1141,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,22 +1171,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emilia Sundell, Hannes Byström</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129678308</v>
+        <v>129678307</v>
       </c>
       <c r="B7" t="n">
-        <v>101004</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1194,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1218,16 +1216,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467285</v>
+        <v>467060</v>
       </c>
       <c r="R7" t="n">
-        <v>6572656</v>
+        <v>6572434</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129678370</v>
+        <v>131509684</v>
       </c>
       <c r="B8" t="n">
-        <v>100909</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,38 +1300,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Holmtorp, Vrm</t>
+          <t>Holmtorp, Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467236</v>
+        <v>467374</v>
       </c>
       <c r="R8" t="n">
-        <v>6572806</v>
+        <v>6572837</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1355,12 +1359,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1375,26 +1389,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129678307</v>
+        <v>131512700</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1415,29 +1429,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Holmtorp, Vrm</t>
+          <t>Holmtorp, Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467060</v>
+        <v>467165</v>
       </c>
       <c r="R9" t="n">
-        <v>6572434</v>
+        <v>6572886</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1461,12 +1471,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1477,26 +1497,51 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Camilla Berglund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emilia Sundell, Hannes Byström</t>
+          <t>Camilla Berglund, Per Arneborn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129678374</v>
+        <v>131521661</v>
       </c>
       <c r="B10" t="n">
-        <v>100909</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,41 +1549,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Holmtorp, Vrm</t>
+          <t>Holmtorp, Karlskoga, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467277</v>
+        <v>467347</v>
       </c>
       <c r="R10" t="n">
-        <v>6572661</v>
+        <v>6572707</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1562,12 +1611,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1582,22 +1636,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129678283</v>
+        <v>129678335</v>
       </c>
       <c r="B11" t="n">
-        <v>100909</v>
+        <v>5179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222771</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1633,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467281</v>
+        <v>467054</v>
       </c>
       <c r="R11" t="n">
-        <v>6572629</v>
+        <v>6572517</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1669,6 +1723,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,52 +1754,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129678306</v>
+        <v>131521670</v>
       </c>
       <c r="B12" t="n">
-        <v>106443</v>
+        <v>5179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220785</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Holmtorp, Vrm</t>
+          <t>Holmtorp, Karlskoga, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467069</v>
+        <v>467249</v>
       </c>
       <c r="R12" t="n">
-        <v>6572443</v>
+        <v>6572853</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1764,12 +1819,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska gnagspår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1778,28 +1838,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emilia Sundell, Hannes Byström</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129678387</v>
+        <v>131521671</v>
       </c>
       <c r="B13" t="n">
-        <v>100909</v>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,41 +1868,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Holmtorp, Vrm</t>
+          <t>Holmtorp, Karlskoga, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467340</v>
+        <v>467173</v>
       </c>
       <c r="R13" t="n">
-        <v>6572633</v>
+        <v>6572829</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1865,12 +1922,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska gnagspår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,18 +1941,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1900,7 +1963,7 @@
         <v>129678334</v>
       </c>
       <c r="B14" t="n">
-        <v>5197</v>
+        <v>5199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,7 +2069,7 @@
         <v>129678386</v>
       </c>
       <c r="B15" t="n">
-        <v>98852</v>
+        <v>99156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2104,27 +2167,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129678372</v>
+        <v>129678364</v>
       </c>
       <c r="B16" t="n">
-        <v>100909</v>
+        <v>101896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>220075</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2134,7 +2197,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2143,10 +2206,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467250</v>
+        <v>467189</v>
       </c>
       <c r="R16" t="n">
-        <v>6572662</v>
+        <v>6572881</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2198,52 +2261,56 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Emilia Sundell, Hannes Byström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131507935</v>
+        <v>129678367</v>
       </c>
       <c r="B17" t="n">
-        <v>91811</v>
+        <v>101896</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220075</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Holmtorp, Holmtorp, Vrm</t>
+          <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467374</v>
+        <v>467207</v>
       </c>
       <c r="R17" t="n">
-        <v>6572837</v>
+        <v>6572817</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2270,22 +2337,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2300,22 +2357,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131509684</v>
+        <v>129678369</v>
       </c>
       <c r="B18" t="n">
-        <v>57911</v>
+        <v>101896</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,39 +2380,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220075</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Holmtorp, Holmtorp, Vrm</t>
+          <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467374</v>
+        <v>467233</v>
       </c>
       <c r="R18" t="n">
-        <v>6572837</v>
+        <v>6572803</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2382,22 +2438,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2412,60 +2458,64 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131521671</v>
+        <v>129678306</v>
       </c>
       <c r="B19" t="n">
-        <v>5179</v>
+        <v>106812</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>220785</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Holmtorp, Karlskoga, Vrm</t>
+          <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467173</v>
+        <v>467069</v>
       </c>
       <c r="R19" t="n">
-        <v>6572829</v>
+        <v>6572443</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2489,17 +2539,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska gnagspår</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2508,72 +2553,70 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Emilia Sundell, Hannes Byström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131512700</v>
+        <v>129678389</v>
       </c>
       <c r="B20" t="n">
-        <v>57911</v>
+        <v>106243</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Holmtorp, Holmtorp, Vrm</t>
+          <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467165</v>
+        <v>467420</v>
       </c>
       <c r="R20" t="n">
-        <v>6572886</v>
+        <v>6572771</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2597,22 +2640,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2623,41 +2656,16 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Camilla Berglund</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Camilla Berglund, Per Arneborn</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2667,7 +2675,7 @@
         <v>131511446</v>
       </c>
       <c r="B21" t="n">
-        <v>97919</v>
+        <v>97983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2771,56 +2779,52 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131521661</v>
+        <v>129678308</v>
       </c>
       <c r="B22" t="n">
-        <v>57911</v>
+        <v>101325</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Holmtorp, Karlskoga, Vrm</t>
+          <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467347</v>
+        <v>467285</v>
       </c>
       <c r="R22" t="n">
-        <v>6572707</v>
+        <v>6572656</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2844,17 +2848,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2869,22 +2868,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Emilia Sundell, Hannes Byström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131521670</v>
+        <v>129678283</v>
       </c>
       <c r="B23" t="n">
-        <v>5179</v>
+        <v>101227</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2892,37 +2891,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>222771</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Holmtorp, Karlskoga, Vrm</t>
+          <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467249</v>
+        <v>467281</v>
       </c>
       <c r="R23" t="n">
-        <v>6572853</v>
+        <v>6572629</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2946,17 +2949,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska gnagspår</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2965,22 +2963,425 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Emilia Sundell, Hannes Byström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129678370</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101227</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Holmtorp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>467236</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6572806</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Emilia Sundell</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Emilia Sundell</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129678372</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101227</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Holmtorp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>467250</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6572662</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Emilia Sundell</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Emilia Sundell</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129678374</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101227</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Holmtorp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>467277</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6572661</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Emilia Sundell</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Emilia Sundell</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129678387</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101227</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Holmtorp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>467340</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6572633</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Emilia Sundell</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Emilia Sundell</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5800-2026 artfynd.xlsx
+++ b/artfynd/A 5800-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131521663</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678333</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678336</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678366</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131507935</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678307</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1398,6 +1433,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131509684</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131512700</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131521661</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1751,6 +1801,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678335</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131521670</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1957,6 +2017,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131521671</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678334</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2164,6 +2234,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678386</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2265,6 +2340,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678364</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2366,6 +2446,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678367</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2467,6 +2552,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678369</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2568,6 +2658,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678306</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2669,6 +2764,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678389</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2776,6 +2876,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131511446</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2877,6 +2982,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678308</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2978,6 +3088,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678283</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3079,6 +3194,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678370</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3180,6 +3300,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678372</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3281,6 +3406,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678374</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3382,8 +3512,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678387</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>